--- a/resultados/angulo/inventario_externos.xlsx
+++ b/resultados/angulo/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4678,6 +4678,111 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://sncr.serpro.gov.br/ccir/emissao?windowId=88e</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>sncr.serpro.gov.br</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://sncr.serpro.gov.br/ccir/emissao?windowId=88e</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/index.php?mod=988&amp;idNot=1453860</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>2</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:02:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://angulo.oxy.elotech.com.br/portaltransparencia/1/publicacoes/1050</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>angulo.oxy.elotech.com.br</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Abrir decreto</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/esic/regulamentacao/regulamentacao</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>3</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:04:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://www.postman.com</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>www.postman.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://diario.angulo.pr.gov.br/swagger/sample</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>3</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:08:29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/angulo/inventario_externos.xlsx
+++ b/resultados/angulo/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4783,6 +4783,41 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://angulo.oxy.elotech.com.br/portaltransparencia/4/licitacoes/detalhes?entidade=4&amp;ex</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>angulo.oxy.elotech.com.br</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://angulo.oxy.elotech.com.br/portaltransparencia/4/licitacoes/detalhes?entidade=4&amp;ex</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://diario.angulo.pr.gov.br/diariooficial/materias/108920251154</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>6</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:45:14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
